--- a/Result/profitability/5450.xlsx
+++ b/Result/profitability/5450.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>0.10125</v>
+        <v>0.11375</v>
       </c>
       <c r="N2" t="n">
-        <v>23.1475</v>
+        <v>23.1675</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -783,7 +783,7 @@
         <v>0.05125</v>
       </c>
       <c r="N3" t="n">
-        <v>20.5325</v>
+        <v>20.44</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,13 +899,13 @@
         <v>0.03</v>
       </c>
       <c r="M4" t="n">
-        <v>0.01125</v>
+        <v>0.04375</v>
       </c>
       <c r="N4" t="n">
-        <v>17.69875</v>
+        <v>17.68625</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-1.12</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.14</v>
+        <v>-0.07750000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>11.8975</v>
+        <v>12.135</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.05</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.115</v>
+        <v>-0.08375</v>
       </c>
       <c r="N6" t="n">
-        <v>10.0275</v>
+        <v>10.4425</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-0.02</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.13</v>
+        <v>-0.1075</v>
       </c>
       <c r="N7" t="n">
-        <v>7.73</v>
+        <v>7.7075</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.12</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.13625</v>
+        <v>-0.10125</v>
       </c>
       <c r="N8" t="n">
-        <v>4.89125</v>
+        <v>4.898750000000001</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1521,7 +1521,7 @@
         <v>-0.15625</v>
       </c>
       <c r="N9" t="n">
-        <v>1.90625</v>
+        <v>1.906250000000001</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -1648,7 +1648,7 @@
         <v>-0.16375</v>
       </c>
       <c r="N10" t="n">
-        <v>1.6625</v>
+        <v>1.662500000000001</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -2026,7 +2026,7 @@
         <v>-0.13</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.045</v>
+        <v>-0.04500000000000001</v>
       </c>
       <c r="N13" t="n">
         <v>6.9475</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5450</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>743</v>
+      </c>
+      <c r="D75" t="n">
+        <v>547</v>
+      </c>
+      <c r="E75" t="n">
+        <v>196</v>
+      </c>
+      <c r="F75" t="n">
+        <v>26.41</v>
+      </c>
+      <c r="G75" t="n">
+        <v>43</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>5.83%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>11</v>
+      </c>
+      <c r="J75" t="n">
+        <v>54</v>
+      </c>
+      <c r="K75" t="n">
+        <v>43</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.15375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>25.8575</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="X75" t="n">
+        <v>3.999999999999999</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.05999999999999872</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.002277039848197271</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-3.333333333333333</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1.899999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.07751937984496116</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
